--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484335_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484335_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8593</v>
+        <v>4.4738</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1403</v>
+        <v>3.6459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7189</v>
+        <v>0.8279</v>
       </c>
       <c r="G2" t="n">
         <v>1.8514</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4061</v>
+        <v>0.2084</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6657</v>
+        <v>-0.1602</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2596</v>
+        <v>0.3686</v>
       </c>
       <c r="V2" t="n">
         <v>1.8279</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0342</v>
+        <v>2.7048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8193</v>
+        <v>1.0431</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2149</v>
+        <v>1.6616</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3335</v>
+        <v>1.557</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2778</v>
+        <v>-0.331</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9443</v>
+        <v>1.8881</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4786</v>
+        <v>1.7815</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1527</v>
+        <v>0.4323</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6741</v>
+        <v>1.3492</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1451</v>
+        <v>-0.2245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1251</v>
+        <v>-0.7634</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2702</v>
+        <v>0.5389</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3491</v>
+        <v>0.5812</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6262</v>
+        <v>0.016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7229</v>
+        <v>0.5653</v>
       </c>
       <c r="V3" t="n">
-        <v>0.719</v>
+        <v>-0.9962</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3321</v>
+        <v>0.2224</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0511</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6793</v>
+        <v>2.3304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8815</v>
+        <v>0.6559</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7978</v>
+        <v>1.6744</v>
       </c>
       <c r="G4" t="n">
-        <v>1.557</v>
+        <v>2.3909</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.331</v>
+        <v>0.0038</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8881</v>
+        <v>2.3871</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7815</v>
+        <v>2.5405</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4323</v>
+        <v>0.5577</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3492</v>
+        <v>1.9828</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2245</v>
+        <v>-0.1496</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7634</v>
+        <v>-0.5538</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5389</v>
+        <v>0.4043</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.5627</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.5395</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.5558</v>
+        <v>0.3302</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1457</v>
+        <v>0.0689</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7014</v>
+        <v>0.2613</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3304</v>
+        <v>2.0291</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6559</v>
+        <v>-0.1313</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6744</v>
+        <v>2.1605</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3909</v>
+        <v>1.3335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0038</v>
+        <v>2.2778</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3871</v>
+        <v>-0.9443</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5405</v>
+        <v>1.4786</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5577</v>
+        <v>2.1527</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9828</v>
+        <v>-0.6741</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1496</v>
+        <v>-0.1451</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5538</v>
+        <v>0.1251</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4043</v>
+        <v>-0.2702</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3302</v>
+        <v>1.344</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0689</v>
+        <v>0.6756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2613</v>
+        <v>0.6685</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.0511</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5928</v>
+        <v>1.556</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9959</v>
+        <v>-0.7332</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5887</v>
+        <v>2.2891</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6569</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2144</v>
+        <v>1.1776</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2529</v>
+        <v>0.0098</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4674</v>
+        <v>1.1678</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0633</v>
+        <v>1.425</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3237</v>
+        <v>1.5201</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3871</v>
+        <v>-0.0951</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4538</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4561</v>
+        <v>0.4106</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9976</v>
+        <v>-0.3241</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7034</v>
+        <v>1.0454</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3019</v>
+        <v>0.9644</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4015</v>
+        <v>0.0809</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2496</v>
+        <v>-0.9589</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1542</v>
+        <v>-0.5538</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4039</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>1.439</v>
+        <v>0.1664</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7238</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.2462</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8843</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1156</v>
+        <v>-2.7688</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2313</v>
+        <v>3.5233</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08649999999999999</v>
+        <v>-1.4538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4106</v>
+        <v>-0.4561</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3241</v>
+        <v>-0.9976</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0454</v>
+        <v>-1.7034</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9644</v>
+        <v>-0.3019</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>-1.4015</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9589</v>
+        <v>0.2496</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5538</v>
+        <v>-0.1542</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>0.4039</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3742</v>
+        <v>1.1301</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4842</v>
+        <v>0.2787</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.8514</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2735</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3253</v>
+        <v>-0.1297</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0503</v>
+        <v>-1.3907</v>
       </c>
       <c r="F9" t="n">
-        <v>1.725</v>
+        <v>1.261</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8927</v>
+        <v>-1.4839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1059</v>
+        <v>-1.6588</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9986</v>
+        <v>0.1749</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1461</v>
+        <v>-1.2643</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7393</v>
+        <v>-1.3047</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0388</v>
+        <v>-0.2196</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6334</v>
+        <v>-0.354</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4054</v>
+        <v>0.1344</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4269</v>
+        <v>0.6314</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4212</v>
+        <v>-0.1265</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0057</v>
+        <v>0.7579</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6642</v>
+        <v>0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4989</v>
+        <v>-0.3387</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2744</v>
+        <v>-2.0909</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7754</v>
+        <v>1.7522</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1979</v>
+        <v>-0.8927</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5344</v>
+        <v>0.1059</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3366</v>
+        <v>-0.9986</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8406</v>
+        <v>0.1461</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6382</v>
+        <v>0.7393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2023</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0384</v>
+        <v>-1.0388</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1727</v>
+        <v>-0.6334</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1342</v>
+        <v>-0.4054</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1798</v>
+        <v>1.4135</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5147</v>
+        <v>0.3806</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6651</v>
+        <v>1.033</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6703</v>
+        <v>-0.9929</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7952</v>
+        <v>-2.5777</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1249</v>
+        <v>1.5848</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4839</v>
+        <v>-0.1979</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6588</v>
+        <v>-0.5344</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1749</v>
+        <v>0.3366</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2643</v>
+        <v>0.8406</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3047</v>
+        <v>0.6382</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>0.2023</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2196</v>
+        <v>-1.0384</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.354</v>
+        <v>-1.1727</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1344</v>
+        <v>0.1342</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.6858</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5309</v>
+        <v>0.2113</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6217</v>
+        <v>0.4745</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5999</v>
+        <v>-2.1603</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0532</v>
+        <v>-1.7498</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5467</v>
+        <v>-0.4105</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8115</v>
@@ -1390,13 +1390,13 @@
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2256</v>
+        <v>0.2139</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2421</v>
+        <v>0.0613</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0165</v>
+        <v>0.1527</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.3492</v>
+        <v>11.652</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.880100000000001</v>
+        <v>-4.5774</v>
       </c>
       <c r="F13" t="n">
-        <v>16.2291</v>
+        <v>16.2292</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7225999999999994</v>
+        <v>0.7225999999999998</v>
       </c>
       <c r="H13" t="n">
         <v>-3.996</v>
       </c>
       <c r="I13" t="n">
-        <v>4.718999999999999</v>
+        <v>4.719</v>
       </c>
       <c r="J13" t="n">
-        <v>6.664799999999999</v>
+        <v>6.6648</v>
       </c>
       <c r="K13" t="n">
         <v>1.9401</v>
@@ -1459,7 +1459,7 @@
         <v>-0.005899999999999905</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.6273</v>
@@ -1468,13 +1468,13 @@
         <v>15.6275</v>
       </c>
       <c r="S13" t="n">
-        <v>7.5801</v>
+        <v>7.882499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0333</v>
+        <v>1.3358</v>
       </c>
       <c r="U13" t="n">
-        <v>6.546799999999999</v>
+        <v>6.5472</v>
       </c>
       <c r="V13" t="n">
         <v>3.0465</v>
@@ -1483,7 +1483,7 @@
         <v>3.0495</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.002899999999999958</v>
+        <v>-0.002900000000000014</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1084</v>
+        <v>4.3028</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1157</v>
+        <v>4.4191</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0073</v>
+        <v>-0.1163</v>
       </c>
       <c r="G14" t="n">
         <v>5.0408</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9091</v>
+        <v>-0.7147</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0289</v>
+        <v>-0.7255</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1198</v>
+        <v>0.0108</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7402</v>
+        <v>2.3963</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9211</v>
+        <v>2.2244</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1809</v>
+        <v>0.1718</v>
       </c>
       <c r="G15" t="n">
         <v>1.4015</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0873</v>
+        <v>-0.4313</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5915</v>
+        <v>-0.2881</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4959</v>
+        <v>-0.1432</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3321</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5793</v>
+        <v>1.6338</v>
       </c>
       <c r="E16" t="n">
         <v>1.0873</v>
       </c>
       <c r="F16" t="n">
-        <v>0.492</v>
+        <v>0.5465</v>
       </c>
       <c r="G16" t="n">
         <v>1.3339</v>
@@ -1702,13 +1702,13 @@
         <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1453</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5484</v>
+        <v>1.0877</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4039</v>
+        <v>-2.9995</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9524</v>
+        <v>4.0872</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0139</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8832</v>
+        <v>-0.3439</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0151</v>
+        <v>-0.6107</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1319</v>
+        <v>0.2667</v>
       </c>
       <c r="V17" t="n">
         <v>0.6642</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0415</v>
+        <v>-0.2905</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1084</v>
+        <v>-0.4117</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1499</v>
+        <v>0.1213</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6424</v>
@@ -1858,13 +1858,13 @@
         <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6482</v>
+        <v>-0.9802</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4015</v>
+        <v>-0.7049</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2467</v>
+        <v>-0.2753</v>
       </c>
       <c r="V18" t="n">
         <v>0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.639</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9538</v>
+        <v>-1.2572</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3148</v>
+        <v>0.3665</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0561</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2471</v>
+        <v>-0.4987</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2943</v>
+        <v>-0.5976</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0472</v>
+        <v>0.0989</v>
       </c>
       <c r="V19" t="n">
         <v>0.6642</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0753</v>
+        <v>-1.8675</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0716</v>
+        <v>-4.7794</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9962</v>
+        <v>2.9118</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0633</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1368</v>
+        <v>0.3446</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4404</v>
+        <v>-0.2674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6964</v>
+        <v>0.612</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1807</v>
+        <v>-1.9614</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.558</v>
+        <v>-1.8657</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3772</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9123</v>
+        <v>-2.2957</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3592</v>
+        <v>0.2262</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5531</v>
+        <v>-2.5219</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7576</v>
+        <v>-0.8575</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2049</v>
+        <v>0.4502</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5527</v>
+        <v>-1.3077</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1546</v>
+        <v>-1.4382</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1542</v>
+        <v>-0.2241</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0004</v>
+        <v>-1.2142</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3857</v>
+        <v>-0.8377</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1594</v>
+        <v>-1.0082</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2262</v>
+        <v>0.1705</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5967</v>
+        <v>-2.0303</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0679</v>
+        <v>-3.7602</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5286999999999999</v>
+        <v>1.7299</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2957</v>
+        <v>-1.9123</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2262</v>
+        <v>-1.3592</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5219</v>
+        <v>-0.5531</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8575</v>
+        <v>-1.7576</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4502</v>
+        <v>-1.2049</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3077</v>
+        <v>-0.5527</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4382</v>
+        <v>-0.1546</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2241</v>
+        <v>-0.1542</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2142</v>
+        <v>-0.0004</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.473</v>
+        <v>-0.2352</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2105</v>
+        <v>-0.3617</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2625</v>
+        <v>0.1265</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6671</v>
+        <v>-4.8697</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8217</v>
+        <v>-4.6194</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8454</v>
+        <v>-0.2503</v>
       </c>
       <c r="G23" t="n">
         <v>0.2104</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.752</v>
+        <v>-0.9547</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1967</v>
+        <v>-0.9944</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5554</v>
+        <v>0.0398</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2081</v>
+        <v>-6.8374</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1494</v>
+        <v>-3.0483</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0587</v>
+        <v>-3.789</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7255</v>
@@ -2326,13 +2326,13 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1858</v>
+        <v>-0.8151</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.8067</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.278</v>
+        <v>-0.0083</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1014</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.3491</v>
+        <v>-9.326799999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-15.0106</v>
       </c>
       <c r="F25" t="n">
-        <v>3.6615</v>
+        <v>5.683700000000002</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7226000000000004</v>
       </c>
       <c r="H25" t="n">
-        <v>3.996100000000002</v>
+        <v>3.996100000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.7187</v>
+        <v>-4.718700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>5.9422</v>
@@ -2383,7 +2383,7 @@
         <v>5.936199999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00599999999999945</v>
+        <v>0.005999999999999672</v>
       </c>
       <c r="M25" t="n">
         <v>-6.6648</v>
@@ -2392,7 +2392,7 @@
         <v>-1.9401</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.724600000000001</v>
+        <v>-4.7246</v>
       </c>
       <c r="P25" t="n">
         <v>0.0001000000000002388</v>
@@ -2404,13 +2404,13 @@
         <v>15.6276</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.579899999999999</v>
+        <v>-5.5577</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.5469</v>
+        <v>-6.5468</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0331</v>
+        <v>0.9892000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.0465</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484335_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484335_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>1.0511</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,7 +895,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -948,7 +978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,714 +1046,760 @@
       </c>
       <c r="X7" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7688</v>
+        <v>0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5233</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4538</v>
+        <v>0.614</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4561</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9976</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7034</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3019</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4015</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2496</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4039</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2787</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8514</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1297</v>
+        <v>0.614</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3907</v>
+        <v>0.614</v>
       </c>
       <c r="F9" t="n">
-        <v>1.261</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4839</v>
+        <v>0.614</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6588</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1749</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2643</v>
+        <v>0.614</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3047</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2196</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6314</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1265</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3387</v>
+        <v>0.307</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0909</v>
+        <v>0.307</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7522</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8927</v>
+        <v>0.307</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1059</v>
+        <v>0.307</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9986</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1461</v>
+        <v>0.307</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7393</v>
+        <v>0.307</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0388</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4135</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3806</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.033</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9929</v>
+        <v>0.1405</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5777</v>
+        <v>-3.3828</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5848</v>
+        <v>3.5233</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1979</v>
+        <v>-2.0677</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5344</v>
+        <v>-1.0701</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3366</v>
+        <v>-0.9976</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8406</v>
+        <v>-2.3174</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6382</v>
+        <v>-0.9159</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2023</v>
+        <v>-1.4015</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0384</v>
+        <v>0.2496</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1727</v>
+        <v>-0.1542</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1342</v>
+        <v>0.4039</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6858</v>
+        <v>1.1301</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2113</v>
+        <v>0.2787</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4745</v>
+        <v>0.8514</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>1.2735</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1603</v>
+        <v>-0.4367</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7498</v>
+        <v>-1.6977</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4105</v>
+        <v>1.261</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8115</v>
+        <v>-1.7909</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3528</v>
+        <v>-1.9658</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4587</v>
+        <v>0.1749</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1423</v>
+        <v>-1.5712</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0614</v>
+        <v>-1.6117</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9538</v>
+        <v>-0.2196</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4142</v>
+        <v>-0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5397</v>
+        <v>0.1344</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2139</v>
+        <v>0.6314</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0613</v>
+        <v>-0.1265</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1527</v>
+        <v>0.7579</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.652</v>
+        <v>-0.9527</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5774</v>
+        <v>-2.7049</v>
       </c>
       <c r="F13" t="n">
-        <v>16.2292</v>
+        <v>1.7522</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7225999999999998</v>
+        <v>-1.5067</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.996</v>
+        <v>-0.5081</v>
       </c>
       <c r="I13" t="n">
-        <v>4.719</v>
+        <v>-0.9986</v>
       </c>
       <c r="J13" t="n">
-        <v>6.6648</v>
+        <v>-0.4678</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9401</v>
+        <v>0.1253</v>
       </c>
       <c r="L13" t="n">
-        <v>4.7245</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.942</v>
+        <v>-1.0388</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.9361</v>
+        <v>-0.6334</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.005899999999999905</v>
+        <v>-0.4054</v>
       </c>
       <c r="P13" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6273</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>15.6275</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>7.882499999999999</v>
+        <v>1.4135</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3358</v>
+        <v>0.3806</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5472</v>
+        <v>1.033</v>
       </c>
       <c r="V13" t="n">
-        <v>3.0465</v>
+        <v>-0.6642</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0495</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.002900000000000014</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BATALLER ABULI</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3028</v>
+        <v>-0.9929</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4191</v>
+        <v>-2.5777</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1163</v>
+        <v>1.5848</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0408</v>
+        <v>-0.1979</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0333</v>
+        <v>-0.5344</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0075</v>
+        <v>0.3366</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8794</v>
+        <v>0.8406</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6017</v>
+        <v>0.6382</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2777</v>
+        <v>0.2023</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8386</v>
+        <v>-1.0384</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5684</v>
+        <v>-1.1727</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2702</v>
+        <v>0.1342</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7147</v>
+        <v>0.6858</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7255</v>
+        <v>0.2113</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0108</v>
+        <v>0.4745</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3963</v>
+        <v>-2.1603</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2244</v>
+        <v>-1.7498</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1718</v>
+        <v>-0.4105</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4015</v>
+        <v>-0.8115</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7667</v>
+        <v>-0.3528</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6348</v>
+        <v>-0.4587</v>
       </c>
       <c r="J15" t="n">
-        <v>1.626</v>
+        <v>0.1423</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1256</v>
+        <v>0.0614</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5004</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2245</v>
+        <v>-0.9538</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3589</v>
+        <v>-0.4142</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>-0.5397</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4313</v>
+        <v>0.2139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2881</v>
+        <v>0.0613</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1432</v>
+        <v>0.1527</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6338</v>
+        <v>11.652</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0873</v>
+        <v>-4.577399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5465</v>
+        <v>16.2292</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3339</v>
+        <v>0.7227000000000005</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3339</v>
+        <v>-3.996</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>4.718999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2689</v>
+        <v>6.665</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2689</v>
+        <v>1.9401</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4.7245</v>
       </c>
       <c r="M16" t="n">
-        <v>0.065</v>
+        <v>-5.942</v>
       </c>
       <c r="N16" t="n">
-        <v>0.065</v>
+        <v>-5.9361</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.005899999999999905</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-15.6273</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>15.6275</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.09080000000000001</v>
+        <v>7.882499999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1816</v>
+        <v>1.3358</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09080000000000001</v>
+        <v>6.5472</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.0465</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.0495</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.002899999999999958</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. BATALLER ABULI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0877</v>
+        <v>4.3028</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9995</v>
+        <v>4.4191</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0872</v>
+        <v>-0.1163</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0139</v>
+        <v>5.0408</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4032</v>
+        <v>2.0333</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4171</v>
+        <v>3.0075</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4121</v>
+        <v>5.8794</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.591</v>
+        <v>2.6017</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8212</v>
+        <v>3.2777</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3982</v>
+        <v>-0.8386</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9942</v>
+        <v>-0.5684</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>-0.2702</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3439</v>
+        <v>-0.7147</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6107</v>
+        <v>-0.7255</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2667</v>
+        <v>0.0108</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6642</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2905</v>
+        <v>2.3963</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4117</v>
+        <v>2.2244</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1213</v>
+        <v>0.1718</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6424</v>
+        <v>1.4015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3697</v>
+        <v>0.7667</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.012</v>
+        <v>0.6348</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4149</v>
+        <v>1.626</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2126</v>
+        <v>1.1256</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2023</v>
+        <v>0.5004</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0573</v>
+        <v>-0.2245</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8429</v>
+        <v>-0.3589</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2144</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9802</v>
+        <v>-0.4313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7049</v>
+        <v>-0.2881</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2753</v>
+        <v>-0.1432</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>R. GUARDIOLA I DISPÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8905999999999999</v>
+        <v>1.8279</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2572</v>
+        <v>1.8279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0561</v>
+        <v>1.8279</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7663</v>
+        <v>1.214</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3172</v>
+        <v>1.8279</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0041</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6869</v>
+        <v>1.214</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3733</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0793</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4987</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5976</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0989</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8675</v>
+        <v>1.6338</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7794</v>
+        <v>1.0873</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9118</v>
+        <v>0.5465</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0633</v>
+        <v>1.3339</v>
       </c>
       <c r="H20" t="n">
-        <v>0.166</v>
+        <v>1.3339</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2294</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9176</v>
+        <v>1.2689</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.284</v>
+        <v>1.2689</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="N20" t="n">
-        <v>0.45</v>
+        <v>0.065</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3446</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2674</v>
+        <v>-0.1816</v>
       </c>
       <c r="U20" t="n">
-        <v>0.612</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9614</v>
+        <v>1.0877</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8657</v>
+        <v>-2.9995</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09569999999999999</v>
+        <v>4.0872</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2957</v>
+        <v>-0.0139</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2262</v>
+        <v>0.4032</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5219</v>
+        <v>-0.4171</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8575</v>
+        <v>-1.4121</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4502</v>
+        <v>-0.591</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>-0.8212</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4382</v>
+        <v>1.3982</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2241</v>
+        <v>0.9942</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2142</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8377</v>
+        <v>-0.3439</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0082</v>
+        <v>-0.6107</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1705</v>
+        <v>0.2667</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0303</v>
+        <v>-0.2905</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7602</v>
+        <v>-0.4117</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7299</v>
+        <v>0.1213</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9123</v>
+        <v>-0.6424</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3592</v>
+        <v>0.3697</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5531</v>
+        <v>-1.012</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7576</v>
+        <v>1.4149</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2049</v>
+        <v>1.2126</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5527</v>
+        <v>0.2023</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1546</v>
+        <v>-2.0573</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1542</v>
+        <v>-0.8429</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0004</v>
+        <v>-1.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2352</v>
+        <v>-0.9802</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3617</v>
+        <v>-0.7049</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1265</v>
+        <v>-0.2753</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6642</v>
+        <v>0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0.8317</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA I DISPÉS</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8697</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6194</v>
+        <v>-1.2572</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2503</v>
+        <v>0.3665</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2104</v>
+        <v>-1.0561</v>
       </c>
       <c r="H23" t="n">
-        <v>0.089</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1214</v>
+        <v>-1.7663</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2586</v>
+        <v>0.3172</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.0041</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6613</v>
+        <v>-0.6869</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0482</v>
+        <v>-1.3733</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5083</v>
+        <v>-0.2939</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5399</v>
+        <v>-1.0793</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.5162</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9547</v>
+        <v>-0.4987</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9944</v>
+        <v>-0.5976</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0398</v>
+        <v>0.0989</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8374</v>
+        <v>-1.8675</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0483</v>
+        <v>-4.7794</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.789</v>
+        <v>2.9118</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7255</v>
+        <v>-0.0633</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7429</v>
+        <v>0.166</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9826</v>
+        <v>-0.2294</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.878</v>
+        <v>-0.9176</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2443</v>
+        <v>-0.284</v>
       </c>
       <c r="L24" t="n">
         <v>-0.6336000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8476</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4986</v>
+        <v>0.45</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.349</v>
+        <v>0.4043</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8151</v>
+        <v>0.3446</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8067</v>
+        <v>-0.2674</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0083</v>
+        <v>0.612</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.1014</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869</v>
+        <v>-0.6642</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7145</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.326799999999999</v>
+        <v>-1.9614</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.0106</v>
+        <v>-1.8657</v>
       </c>
       <c r="F25" t="n">
-        <v>5.683700000000002</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7226000000000004</v>
+        <v>-2.2957</v>
       </c>
       <c r="H25" t="n">
-        <v>3.996100000000001</v>
+        <v>0.2262</v>
       </c>
       <c r="I25" t="n">
+        <v>-2.5219</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.8575</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.4382</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2241</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.2142</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.8377</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1.0082</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. NOGUER SANTAELLA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.0303</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.7602</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.7299</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.9123</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.3592</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.7576</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.2049</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.1546</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.1542</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2352</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3617</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R. GUARDIOLA I DISPES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-6.6977</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.4474</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.2503</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.6175</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.5249</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.0926</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.5694</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.0482</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.5083</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.9547</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.9944</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>J. CALLAVE FERRER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-6.8374</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.0483</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-3.789</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.7255</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.7429</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.9826</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.878</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.2443</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.8476</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.4986</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-1.349</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.8151</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.8067</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-3.1014</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484335_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-9.3269</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-15.0107</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.6837</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.7226000000000012</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.996200000000001</v>
+      </c>
+      <c r="I29" t="n">
         <v>-4.718700000000001</v>
       </c>
-      <c r="J25" t="n">
-        <v>5.9422</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="J29" t="n">
+        <v>5.9421</v>
+      </c>
+      <c r="K29" t="n">
         <v>5.936199999999999</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L29" t="n">
         <v>0.005999999999999672</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-6.6648</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-1.9401</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>-4.7246</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.0001000000000002388</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P29" t="n">
+        <v>9.99999999997947e-05</v>
+      </c>
+      <c r="Q29" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>15.6276</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>-5.5577</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>-6.5468</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>0.9892000000000001</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>-3.0465</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>1.2215</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-4.268</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
